--- a/source/exclusive_listings.xlsx
+++ b/source/exclusive_listings.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24260" windowHeight="12420"/>
+    <workbookView windowWidth="27780" windowHeight="16040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>MLS Number</t>
   </si>
   <si>
     <t>Property Address</t>
-  </si>
-  <si>
-    <t>Represents</t>
   </si>
   <si>
     <t>Beds</t>
@@ -47,25 +44,382 @@
     <t>Sq Ft</t>
   </si>
   <si>
-    <t>Listing Date</t>
+    <t>Listing Price</t>
   </si>
   <si>
-    <t>Sale Date</t>
-  </si>
-  <si>
-    <t>Days on Market</t>
-  </si>
-  <si>
-    <t>Sale/Lease Price</t>
-  </si>
-  <si>
-    <t>415 East 37th Street #11A</t>
-  </si>
-  <si>
-    <t>Buyer</t>
+    <t>Features</t>
   </si>
   <si>
     <t>26 Avenue At Port Imperial APT 416, West New York, NJ 07093</t>
+  </si>
+  <si>
+    <r>
+      <t>- Rare 2BR + loft penthouse with soaring 20’ ceilings and bright southwest exposure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Sun-drenched interior with freshly sanded hardwood floors and open-concept layout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Chef’s kitchen with JennAir stainless steel appliances and abundant cabinetry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Primary suite with walk-in closet and full bath, plus versatile loft for office or guest space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- In-unit washer/dryer, brand new boiler (2025), and deeded indoor parking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Resort-style amenities including pool, fitness center, tennis courts, basketball court, and dog run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime commuter location near ferry, bus, and Light Rail</t>
+    </r>
+  </si>
+  <si>
+    <t>S1785517</t>
+  </si>
+  <si>
+    <t>343 E 74th St #Ph2B, New York, NY 10021</t>
+  </si>
+  <si>
+    <r>
+      <t>- Penthouse corner 2BR/2.5BA condop with private balcony and open city views</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Sun-filled layout with 9’ ceilings and ~1,100 SF of living space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Open kitchen flowing into dining and expansive living area—ideal for entertaining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Flexible ownership with no board approval and subletting allowed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Full-service, pet-friendly building with 24-hour doorman and on-site staff</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Amenities include fitness center, roof deck, concierge, and garage access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime Upper East Side location near dining, shopping, and transportation</t>
+    </r>
+  </si>
+  <si>
+    <t>S1800899</t>
+  </si>
+  <si>
+    <t>415 E 37th St APT 11A, New York, NY 10016</t>
+  </si>
+  <si>
+    <r>
+      <t>- Newly renovated 1-bedroom (potential 1BR + den) with stunning East River views</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Sun-filled 860 SF layout with oversized windows and wide-plank hardwood floors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Excellent storage including walk-in closet and potential for in-unit washer/dryer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Full-service, white-glove building with 24-hour doorman and concierge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Extensive amenities including rooftop pool, fitness centers, spa, and screening room</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime Murray Hill location near parks, Trader Joe’s, Grand Central, and major transit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Convenient access to FDR Drive, Midtown Tunnel, and ferry service</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -79,7 +433,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,26 +442,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF444746"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Roboto"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -254,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,12 +608,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF356854"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -454,7 +811,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -463,17 +820,167 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color rgb="FF356854"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,70 +1102,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -667,10 +1168,10 @@
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -679,10 +1180,10 @@
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -691,10 +1192,10 @@
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,10 +1204,10 @@
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -715,62 +1216,82 @@
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="26" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1297,101 +1818,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="13.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="39.0961538461538" customWidth="1"/>
-    <col min="11" max="11" width="12.5384615384615"/>
+    <col min="2" max="2" width="36.5288461538462" customWidth="1"/>
+    <col min="3" max="3" width="55.125" customWidth="1"/>
+    <col min="6" max="6" width="20.8269230769231" customWidth="1"/>
+    <col min="7" max="7" width="33.9615384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1">
+    <row r="1" ht="31.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:7">
+      <c r="A2" s="4">
+        <v>26006906</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1121</v>
+      </c>
+      <c r="F2" s="14">
+        <v>780000</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:7">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1111</v>
+      </c>
+      <c r="F3" s="16">
+        <v>1020000</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="12">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="E4" s="12">
         <v>860</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="6">
+      <c r="F4" s="18">
         <v>1260000</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1121</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="6">
-        <v>780000</v>
+      <c r="G4" s="19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/source/exclusive_listings.xlsx
+++ b/source/exclusive_listings.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27780" windowHeight="16040"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>MLS Number</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Rare 2BR + loft penthouse with soaring 20’ ceilings and bright southwest exposure</t>
     </r>
     <r>
@@ -179,6 +185,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Penthouse corner 2BR/2.5BA condop with private balcony and open city views</t>
     </r>
     <r>
@@ -295,15 +307,18 @@
       </rPr>
       <t>- Prime Upper East Side location near dining, shopping, and transportation</t>
     </r>
-  </si>
-  <si>
-    <t>S1800899</t>
   </si>
   <si>
     <t>415 E 37th St APT 11A, New York, NY 10016</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Newly renovated 1-bedroom (potential 1BR + den) with stunning East River views</t>
     </r>
     <r>
@@ -851,6 +866,21 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF284E3F"/>
       </left>
       <right style="medium">
@@ -870,6 +900,21 @@
       </left>
       <right style="medium">
         <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
@@ -936,36 +981,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF6F8F9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1245,49 +1260,49 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1821,6 +1836,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
+    <col min="1" max="1" width="16.3365384615385" customWidth="1"/>
     <col min="2" max="2" width="36.5288461538462" customWidth="1"/>
     <col min="3" max="3" width="55.125" customWidth="1"/>
     <col min="6" max="6" width="20.8269230769231" customWidth="1"/>
@@ -1846,77 +1862,77 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:7">
-      <c r="A2" s="4">
+    <row r="2" ht="304.75" spans="1:7">
+      <c r="A2" s="5">
         <v>26006906</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>2</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <v>2</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>1121</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="8">
         <v>780000</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:7">
-      <c r="A3" s="7" t="s">
+    <row r="3" ht="289.75" spans="1:7">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="12">
         <v>2</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="12">
         <v>2.5</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>1111</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="13">
         <v>1020000</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:7">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="304.75" spans="1:7">
+      <c r="A4" s="15">
+        <v>11607803</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="C4" s="17">
         <v>1</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="17">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="17">
         <v>860</v>
       </c>
       <c r="F4" s="18">
         <v>1260000</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
